--- a/5/search/FY3_Missile1_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY3_Missile1_results/fine_tuned/comparison.xlsx
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="C3" t="n">
-        <v>131.3</v>
+        <v>128.8</v>
       </c>
       <c r="D3" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F3" t="n">
         <v>3.100000000000001</v>

--- a/5/search/FY3_Missile1_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY3_Missile1_results/fine_tuned/comparison.xlsx
@@ -467,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="C2" t="n">
-        <v>128.8</v>
+        <v>112</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>128.8</v>
+        <v>131.4</v>
       </c>
       <c r="D3" t="n">
-        <v>20.6</v>
+        <v>23.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>3.100000000000001</v>
+        <v>3.200000000000003</v>
       </c>
     </row>
   </sheetData>
